--- a/artfynd/A 39553-2024 artfynd.xlsx
+++ b/artfynd/A 39553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119715682</v>
+        <v>119715661</v>
       </c>
       <c r="B2" t="n">
-        <v>57986</v>
+        <v>58013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455057</v>
+        <v>454849</v>
       </c>
       <c r="R2" t="n">
-        <v>6522241</v>
+        <v>6522261</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119715649</v>
+        <v>119715673</v>
       </c>
       <c r="B3" t="n">
         <v>58013</v>
@@ -830,7 +830,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454929</v>
+        <v>454952</v>
       </c>
       <c r="R3" t="n">
-        <v>6522280</v>
+        <v>6522266</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119715661</v>
+        <v>119715662</v>
       </c>
       <c r="B4" t="n">
         <v>58013</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454849</v>
+        <v>455014</v>
       </c>
       <c r="R4" t="n">
-        <v>6522261</v>
+        <v>6522252</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119715673</v>
+        <v>119715364</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>57643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454952</v>
+        <v>454931</v>
       </c>
       <c r="R5" t="n">
-        <v>6522266</v>
+        <v>6522331</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119715364</v>
+        <v>119715682</v>
       </c>
       <c r="B6" t="n">
-        <v>57643</v>
+        <v>57986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,20 +1147,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454931</v>
+        <v>455057</v>
       </c>
       <c r="R6" t="n">
-        <v>6522331</v>
+        <v>6522241</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119715662</v>
+        <v>119715649</v>
       </c>
       <c r="B7" t="n">
         <v>58013</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455014</v>
+        <v>454929</v>
       </c>
       <c r="R7" t="n">
-        <v>6522252</v>
+        <v>6522280</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 39553-2024 artfynd.xlsx
+++ b/artfynd/A 39553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119715661</v>
+        <v>119715682</v>
       </c>
       <c r="B2" t="n">
-        <v>58013</v>
+        <v>57986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454849</v>
+        <v>455057</v>
       </c>
       <c r="R2" t="n">
-        <v>6522261</v>
+        <v>6522241</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119715673</v>
+        <v>119715364</v>
       </c>
       <c r="B3" t="n">
-        <v>58013</v>
+        <v>57643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454952</v>
+        <v>454931</v>
       </c>
       <c r="R3" t="n">
-        <v>6522266</v>
+        <v>6522331</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119715364</v>
+        <v>119715649</v>
       </c>
       <c r="B5" t="n">
-        <v>57643</v>
+        <v>58013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454931</v>
+        <v>454929</v>
       </c>
       <c r="R5" t="n">
-        <v>6522331</v>
+        <v>6522280</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119715682</v>
+        <v>119715673</v>
       </c>
       <c r="B6" t="n">
-        <v>57986</v>
+        <v>58013</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,25 +1147,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455057</v>
+        <v>454952</v>
       </c>
       <c r="R6" t="n">
-        <v>6522241</v>
+        <v>6522266</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119715649</v>
+        <v>119715661</v>
       </c>
       <c r="B7" t="n">
         <v>58013</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454929</v>
+        <v>454849</v>
       </c>
       <c r="R7" t="n">
-        <v>6522280</v>
+        <v>6522261</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 39553-2024 artfynd.xlsx
+++ b/artfynd/A 39553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119715682</v>
+        <v>119715662</v>
       </c>
       <c r="B2" t="n">
-        <v>57986</v>
+        <v>58013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455057</v>
+        <v>455014</v>
       </c>
       <c r="R2" t="n">
-        <v>6522241</v>
+        <v>6522252</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119715364</v>
+        <v>119715661</v>
       </c>
       <c r="B3" t="n">
-        <v>57643</v>
+        <v>58013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454931</v>
+        <v>454849</v>
       </c>
       <c r="R3" t="n">
-        <v>6522331</v>
+        <v>6522261</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119715662</v>
+        <v>119715682</v>
       </c>
       <c r="B4" t="n">
-        <v>58013</v>
+        <v>57986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455014</v>
+        <v>455057</v>
       </c>
       <c r="R4" t="n">
-        <v>6522252</v>
+        <v>6522241</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119715649</v>
+        <v>119715364</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>57643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454929</v>
+        <v>454931</v>
       </c>
       <c r="R5" t="n">
-        <v>6522280</v>
+        <v>6522331</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119715661</v>
+        <v>119715649</v>
       </c>
       <c r="B7" t="n">
         <v>58013</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454849</v>
+        <v>454929</v>
       </c>
       <c r="R7" t="n">
-        <v>6522261</v>
+        <v>6522280</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 39553-2024 artfynd.xlsx
+++ b/artfynd/A 39553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119715662</v>
+        <v>119715682</v>
       </c>
       <c r="B2" t="n">
-        <v>58013</v>
+        <v>57996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455014</v>
+        <v>455057</v>
       </c>
       <c r="R2" t="n">
-        <v>6522252</v>
+        <v>6522241</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119715661</v>
+        <v>119715673</v>
       </c>
       <c r="B3" t="n">
-        <v>58013</v>
+        <v>58023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454849</v>
+        <v>454952</v>
       </c>
       <c r="R3" t="n">
-        <v>6522261</v>
+        <v>6522266</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119715682</v>
+        <v>119715662</v>
       </c>
       <c r="B4" t="n">
-        <v>57986</v>
+        <v>58023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455057</v>
+        <v>455014</v>
       </c>
       <c r="R4" t="n">
-        <v>6522241</v>
+        <v>6522252</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119715364</v>
+        <v>119715661</v>
       </c>
       <c r="B5" t="n">
-        <v>57643</v>
+        <v>58023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454931</v>
+        <v>454849</v>
       </c>
       <c r="R5" t="n">
-        <v>6522331</v>
+        <v>6522261</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119715673</v>
+        <v>119715649</v>
       </c>
       <c r="B6" t="n">
-        <v>58013</v>
+        <v>58023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454952</v>
+        <v>454929</v>
       </c>
       <c r="R6" t="n">
-        <v>6522266</v>
+        <v>6522280</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119715649</v>
+        <v>119715364</v>
       </c>
       <c r="B7" t="n">
-        <v>58013</v>
+        <v>57653</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454929</v>
+        <v>454931</v>
       </c>
       <c r="R7" t="n">
-        <v>6522280</v>
+        <v>6522331</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 39553-2024 artfynd.xlsx
+++ b/artfynd/A 39553-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119715682</v>
+        <v>119715441</v>
       </c>
       <c r="B2" t="n">
-        <v>57996</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102987</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +710,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455057</v>
+        <v>454807</v>
       </c>
       <c r="R2" t="n">
-        <v>6522241</v>
+        <v>6522276</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119715673</v>
+        <v>119715364</v>
       </c>
       <c r="B3" t="n">
-        <v>58023</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +820,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454952</v>
+        <v>454931</v>
       </c>
       <c r="R3" t="n">
-        <v>6522266</v>
+        <v>6522331</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,37 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119715662</v>
+        <v>119715682</v>
       </c>
       <c r="B4" t="n">
-        <v>58023</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +930,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455014</v>
+        <v>455057</v>
       </c>
       <c r="R4" t="n">
-        <v>6522252</v>
+        <v>6522241</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,12 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119715661</v>
+        <v>119715649</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,7 +1040,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454849</v>
+        <v>454929</v>
       </c>
       <c r="R5" t="n">
-        <v>6522261</v>
+        <v>6522280</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,12 +1079,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119715649</v>
+        <v>119715661</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1150,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454929</v>
+        <v>454849</v>
       </c>
       <c r="R6" t="n">
-        <v>6522280</v>
+        <v>6522261</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,12 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119715364</v>
+        <v>119715662</v>
       </c>
       <c r="B7" t="n">
-        <v>57653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454931</v>
+        <v>455014</v>
       </c>
       <c r="R7" t="n">
-        <v>6522331</v>
+        <v>6522252</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1362,6 +1332,223 @@
           <t>Ecogain</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119715673</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ingelstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>454952</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6522266</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hova</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122234241</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ebbetorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>455402</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6522364</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hova</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Inspelad med autobox Pettersson D500X.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
